--- a/Outputs/Scenarios/PtX_demand_ES_Methanol.xlsx
+++ b/Outputs/Scenarios/PtX_demand_ES_Methanol.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.001803265043043054</v>
       </c>
       <c r="K16" t="n">
-        <v>0.01614790245846248</v>
+        <v>0.01785131107648858</v>
       </c>
     </row>
     <row r="17">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.02691317076410414</v>
+        <v>0.02518252131620379</v>
       </c>
     </row>
     <row r="19">
@@ -1481,7 +1481,7 @@
         <v>2.598199685446796e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>0.01076526830564165</v>
+        <v>0.01079250913551591</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.002669514355199396</v>
       </c>
       <c r="K30" t="n">
-        <v>0.08703958879574604</v>
+        <v>0.09622121384243575</v>
       </c>
     </row>
     <row r="31">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.1450659813262434</v>
+        <v>0.1357375241670357</v>
       </c>
     </row>
     <row r="33">
@@ -1999,7 +1999,7 @@
         <v>0.0001405007555368104</v>
       </c>
       <c r="K42" t="n">
-        <v>0.05802639253049736</v>
+        <v>0.05817322464301532</v>
       </c>
     </row>
     <row r="43">
